--- a/quizzes/peinture-14e-niveau2.xlsx
+++ b/quizzes/peinture-14e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7408A4B2-B387-4B7B-9439-B1D8155E5050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B25886AA-6127-42D3-928A-87EC1285F926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="363">
   <si>
     <t>image</t>
   </si>
@@ -37,6 +37,15 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
+    <t>dates artiste</t>
+  </si>
+  <si>
+    <t>Matériaux et technique</t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a8/Florence%2C_Santa_Croce%2C_apse%2C_Legend_of_the_True_Cross%2C_frescoe_cycle_by_Agnolo_Gaddi%2C_1385-1387_north.jpg/1280px-Florence%2C_Santa_Croce%2C_apse%2C_Legend_of_the_True_Cross%2C_frescoe_cycle_by_Agnolo_Gaddi%2C_1385-1387_north.jpg</t>
   </si>
   <si>
@@ -52,6 +61,15 @@
     <t>Légende de la Vraie Croix (fresques)</t>
   </si>
   <si>
+    <t>vers 1350-1396</t>
+  </si>
+  <si>
+    <t>Fresque</t>
+  </si>
+  <si>
+    <t>dimensions architecturales</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg/960px-An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -67,6 +85,15 @@
     <t>Miraj Nameh (Un ange offre une ville au Prophète)</t>
   </si>
   <si>
+    <t>actif vers 1330-1340 (dates incertaines)</t>
+  </si>
+  <si>
+    <t>Encre, couleurs et or sur papier</t>
+  </si>
+  <si>
+    <t>dimensions non standardisées</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/3_Allegretto_Nuzi._Coronation_of_the_Virgin%2C_ca._1350._Southampton_City_Art_Gallery..jpg/1280px-3_Allegretto_Nuzi._Coronation_of_the_Virgin%2C_ca._1350._Southampton_City_Art_Gallery..jpg</t>
   </si>
   <si>
@@ -82,6 +109,12 @@
     <t>Le Couronnement de la Vierge</t>
   </si>
   <si>
+    <t>vers 1370-vers 1425</t>
+  </si>
+  <si>
+    <t>Tempera sur bois</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/68/Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg/1280px-Padova%2C_basilica_di_Sant%27Antonio_-_Cappella_di_San_Giacomo_-_Affreschi_03.jpg</t>
   </si>
   <si>
@@ -97,6 +130,9 @@
     <t>Fresques de la chapelle San Giacomo</t>
   </si>
   <si>
+    <t>vers 1330-vers 1390</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg/1280px-Ambrogio_Lorenzetti_-_Effects_of_Good_Government_in_the_city_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -112,6 +148,9 @@
     <t>Allégorie et effets du Bon et du Mauvais Gouvernement</t>
   </si>
   <si>
+    <t>vers 1290-1348</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a2/Andr%C3%A9_Beauneveu_-_King_David_-_WGA1531.jpg/1280px-Andr%C3%A9_Beauneveu_-_King_David_-_WGA1531.jpg</t>
   </si>
   <si>
@@ -127,6 +166,12 @@
     <t>Le Roi David (Psautier de Jean de Berry)</t>
   </si>
   <si>
+    <t>Enluminure sur parchemin</t>
+  </si>
+  <si>
+    <t>petit format manuscrit</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/0e/Museo_di_santa_maria_novella%2C_cappellone_degli_spagnoli%2C_affreschi_di_andrea_di_bonaiuto_8.JPG/1280px-Museo_di_santa_maria_novella%2C_cappellone_degli_spagnoli%2C_affreschi_di_andrea_di_bonaiuto_8.JPG</t>
   </si>
   <si>
@@ -142,6 +187,9 @@
     <t>Fresques de la Chapelle des Espagnols</t>
   </si>
   <si>
+    <t>actif 1343-1377</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f3/Madonna_of_Humility%2C_The_Blessing_Christ%2C_Two_Angels%2C_and_a_Donor_%28obverse%29_A16766.jpg/1280px-Madonna_of_Humility%2C_The_Blessing_Christ%2C_Two_Angels%2C_and_a_Donor_%28obverse%29_A16766.jpg</t>
   </si>
   <si>
@@ -157,6 +205,9 @@
     <t>Madone de l'Humilité avec le Christ bénissant, deux anges et un donateur</t>
   </si>
   <si>
+    <t>vers 1360-1428</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/8_Andrea_di_Cione_Orcagna%2C_Strozzi_Altarpiece._1354-57%2C_Santa_Maria_Novella%2C_Florence..jpeg/1280px-8_Andrea_di_Cione_Orcagna%2C_Strozzi_Altarpiece._1354-57%2C_Santa_Maria_Novella%2C_Florence..jpeg</t>
   </si>
   <si>
@@ -169,6 +220,9 @@
     <t>Retable Strozzi</t>
   </si>
   <si>
+    <t>vers 1308-1368</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/91/Bartolo_di_Fredi_-_Adoration_of_the_Magi.jpg/1280px-Bartolo_di_Fredi_-_Adoration_of_the_Magi.jpg</t>
   </si>
   <si>
@@ -184,6 +238,9 @@
     <t>Adoration des mages</t>
   </si>
   <si>
+    <t>vers 1330-1410</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/Bartolomeo_bulgarini%2C_madonna_col_bambino_e_i_sa_nti_ansano_e_galgano.JPG/1280px-Bartolomeo_bulgarini%2C_madonna_col_bambino_e_i_sa_nti_ansano_e_galgano.JPG</t>
   </si>
   <si>
@@ -193,6 +250,9 @@
     <t>Madone à l'Enfant avec saint Ansano et saint Galgano</t>
   </si>
   <si>
+    <t>actif vers 1337-1378</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg/960px-Bernardo_Dadd_1347i%2C_MAdone_de_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -208,6 +268,9 @@
     <t>Vierge à l'Enfant en trône (Madone d'Orsanmichele)</t>
   </si>
   <si>
+    <t>vers 1280-1348</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4a/Cimabue_-_Maest%C3%A0_di_Santa_Trinita_-_Google_Art_Project.jpg/1280px-Cimabue_-_Maest%C3%A0_di_Santa_Trinita_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -220,6 +283,12 @@
     <t>Maestà di Santa Trinita</t>
   </si>
   <si>
+    <t>vers 1240-1302</t>
+  </si>
+  <si>
+    <t>385 × 223 cm</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/22/1403_Altarbild_Conrad_von_Soest.jpg/1280px-1403_Altarbild_Conrad_von_Soest.jpg</t>
   </si>
   <si>
@@ -235,6 +304,9 @@
     <t>Retable de Wildungen</t>
   </si>
   <si>
+    <t>vers 1370-après 1422</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/Duccio_Maest%C3%A0.jpg/1280px-Duccio_Maest%C3%A0.jpg</t>
   </si>
   <si>
@@ -250,6 +322,12 @@
     <t>La Maestà</t>
   </si>
   <si>
+    <t>vers 1255-vers 1318</t>
+  </si>
+  <si>
+    <t>dimensions architecturales (polyptyque)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d7/Monastery_of_Pedralbes%2C_frescoes_painted_in_1346_by_Ferrer_Bassa_in_the_Capella_de_Sant_Miquel_%282%29_%2831215371495%29.jpg/1280px-Monastery_of_Pedralbes%2C_frescoes_painted_in_1346_by_Ferrer_Bassa_in_the_Capella_de_Sant_Miquel_%282%29_%2831215371495%29.jpg</t>
   </si>
   <si>
@@ -265,6 +343,27 @@
     <t>Fresques de la chapelle Saint-Michel</t>
   </si>
   <si>
+    <t>vers 1285-1348</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Francesco_Traini_Pisa_01.JPG</t>
+  </si>
+  <si>
+    <t>Francesco Traini</t>
+  </si>
+  <si>
+    <t>1345</t>
+  </si>
+  <si>
+    <t>Museo Nazionale di San Matteo, Pise</t>
+  </si>
+  <si>
+    <t>Polyptyque de San Domenico (avec saint Dominique)</t>
+  </si>
+  <si>
+    <t>actif 1321-vers 1363</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Giotto_-_Scrovegni_-_-36-_-_Lamentation_%28The_Mourning_of_Christ%29_adj.jpg/1280px-Giotto_-_Scrovegni_-_-36-_-_Lamentation_%28The_Mourning_of_Christ%29_adj.jpg</t>
   </si>
   <si>
@@ -280,6 +379,9 @@
     <t>Lamentation (La Mourning du Christ)</t>
   </si>
   <si>
+    <t>vers 1267-1337</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/35/Giovanni_da_milano%2C_piet%C3%A0.jpg/1280px-Giovanni_da_milano%2C_piet%C3%A0.jpg</t>
   </si>
   <si>
@@ -292,6 +394,9 @@
     <t>Pietà</t>
   </si>
   <si>
+    <t>actif vers 1346-1369</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/25/Battistero_Padova_-_00view.jpg/1280px-Battistero_Padova_-_00view.jpg</t>
   </si>
   <si>
@@ -307,6 +412,27 @@
     <t>Le Couronnement de la Vierge (coupole)</t>
   </si>
   <si>
+    <t>actif 1349-vers 1391</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG/1280px-Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG</t>
+  </si>
+  <si>
+    <t>Guariento di Arpo</t>
+  </si>
+  <si>
+    <t>1344</t>
+  </si>
+  <si>
+    <t>Norton Simon Museum, Pasadena</t>
+  </si>
+  <si>
+    <t>Le Couronnement de la Vierge (retable)</t>
+  </si>
+  <si>
+    <t>vers 1310-vers 1370</t>
+  </si>
+  <si>
     <t>https://commons.wikimedia.org/wiki/File:%E5%AF%8C%E6%98%A5%E5%B1%B1%E5%B1%85%E5%9C%96(%E7%84%A1%E7%94%A8%E5%B8%AB%E5%8D%B7).jpg#/media/File:Huang_Gongwang._Dwelling_in_the_Fuchun_Mountains._detail._National_Palace_Museum,_Taipei.jpg</t>
   </si>
   <si>
@@ -322,6 +448,15 @@
     <t>Habitation dans les monts Fuchun</t>
   </si>
   <si>
+    <t>1269-1354</t>
+  </si>
+  <si>
+    <t>Encre sur papier (rouleau)</t>
+  </si>
+  <si>
+    <t>environ 33 × 636 cm</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7b/2_Jacopo_di_Cione_Polyptych_San_Pier_Maggiore%2C_detail._1370-71_London_NG.jpg/1280px-2_Jacopo_di_Cione_Polyptych_San_Pier_Maggiore%2C_detail._1370-71_London_NG.jpg</t>
   </si>
   <si>
@@ -337,6 +472,9 @@
     <t>Couronnement de la Vierge (San Pier Maggiore Altarpiece)</t>
   </si>
   <si>
+    <t>actif vers 1362-1398</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/11/Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg/1280px-Jaume_Serra_-_Altarpiece_of_the_Virgin_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -352,6 +490,33 @@
     <t>Retable de la Vierge de Sixena</t>
   </si>
   <si>
+    <t>actif 1358-vers 1389</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Jean_De_Beaumetz_-_Christ_on_the_Cross_with_a_Carthusian_Monk_-_WGA11944.jpg/1280px-Jean_De_Beaumetz_-_Christ_on_the_Cross_with_a_Carthusian_Monk_-_WGA11944.jpg</t>
+  </si>
+  <si>
+    <t>Jean de Beaumetz</t>
+  </si>
+  <si>
+    <t>1389-1395</t>
+  </si>
+  <si>
+    <t>Cleveland Museum of Art</t>
+  </si>
+  <si>
+    <t>Calvaire avec un moine chartreux</t>
+  </si>
+  <si>
+    <t>?-1396</t>
+  </si>
+  <si>
+    <t>Huile sur bois</t>
+  </si>
+  <si>
+    <t>58,7 × 47,2 cm</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg/1280px-4_Jean_Pucelle._Hours_of_Jeanne_d%27Evreux._1325-28%2C_Metropolitan_Museum%2C_New-York.jpg</t>
   </si>
   <si>
@@ -367,6 +532,12 @@
     <t>Les Heures de Jeanne d'Évreux</t>
   </si>
   <si>
+    <t>actif 1319-vers 1334</t>
+  </si>
+  <si>
+    <t>Enluminure, encre et grisaille sur parchemin</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/Ka%C5%8D_Ninga_-_Priest_Xian-zi_catching_shrimp.jpg/1280px-Ka%C5%8D_Ninga_-_Priest_Xian-zi_catching_shrimp.jpg</t>
   </si>
   <si>
@@ -382,6 +553,12 @@
     <t>Xianzi capturant une crevette</t>
   </si>
   <si>
+    <t>actif début-milieu 14e siècle (dates incertaines)</t>
+  </si>
+  <si>
+    <t>Encre sur papier</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg/1280px-Measta._lippo_memmi%2C_palazzo_comunale_in_san_gimignano.jpg</t>
   </si>
   <si>
@@ -397,6 +574,9 @@
     <t>Maestà (fresque)</t>
   </si>
   <si>
+    <t>actif 1317-vers 1356</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7e/Lorenzo_Monaco_-_Incoronazione_della_Vergine_-_Google_Art_Project.jpg/1280px-Lorenzo_Monaco_-_Incoronazione_della_Vergine_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -421,6 +601,9 @@
     <t>Retable de l'Annonciation (Polittico dell'Annunciazione)</t>
   </si>
   <si>
+    <t>actif 1356-1372</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7a/Wilton_diptych.jpg/1280px-Wilton_diptych.jpg</t>
   </si>
   <si>
@@ -433,6 +616,12 @@
     <t>Le Diptyque Wilton</t>
   </si>
   <si>
+    <t>anonyme, actif fin 14e siècle</t>
+  </si>
+  <si>
+    <t>53 × 37 cm (chaque panneau)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ac/%CE%A0%CF%81%CF%89%CF%84%CE%AC%CF%84%CE%BF_-_%CE%A4%CE%BF%CE%B9%CF%87%CE%BF%CE%B3%CF%81%CE%B1%CF%86%CE%AF%CE%B5%CF%82.jpg/1280px-%CE%A0%CF%81%CF%89%CF%84%CE%AC%CF%84%CE%BF_-_%CE%A4%CE%BF%CE%B9%CF%87%CE%BF%CE%B3%CF%81%CE%B1%CF%86%CE%AF%CE%B5%CF%82.jpg</t>
   </si>
   <si>
@@ -445,6 +634,9 @@
     <t>Fresques du catholicon</t>
   </si>
   <si>
+    <t>actif fin 13e-début 14e siècle (dates incertaines)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a8/S._croce%2C_cappella_bardi_di_vernio_01.jpg/1280px-S._croce%2C_cappella_bardi_di_vernio_01.jpg</t>
   </si>
   <si>
@@ -457,6 +649,9 @@
     <t>Fresques de la chapelle Bardi di Vernio (Vie de saint Sylvestre)</t>
   </si>
   <si>
+    <t>actif vers 1320-1350</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/c9/Meister_Bertram_von_Minden_-_Grabow_Altarpiece_-_WGA14309.jpg/1280px-Meister_Bertram_von_Minden_-_Grabow_Altarpiece_-_WGA14309.jpg</t>
   </si>
   <si>
@@ -472,6 +667,9 @@
     <t>Retable de Grabow</t>
   </si>
   <si>
+    <t>vers 1340-1414</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9a/1426_Meister_Francke_Die_Anbetung_des_Kindes_anagoria.JPG/1280px-1426_Meister_Francke_Die_Anbetung_des_Kindes_anagoria.JPG</t>
   </si>
   <si>
@@ -484,6 +682,9 @@
     <t>L'Adoration de l'Enfant (Retable de saint Thomas)</t>
   </si>
   <si>
+    <t>vers 1380-vers 1436</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e1/Master_of_the_Vy%C5%A1%C5%A1%C3%AD_Brod_Altarpiece_-_Nativity_-_Google_Art_Project.jpg/1280px-Master_of_the_Vy%C5%A1%C5%A1%C3%AD_Brod_Altarpiece_-_Nativity_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -499,6 +700,9 @@
     <t>Nativité (cycle du Retable de Vyšší Brod)</t>
   </si>
   <si>
+    <t>anonyme, actif vers 1350</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/17/Olt%C3%A1%C5%99_t%C5%99ebo%C5%88sk%C3%BD%2C_Kristus_na_ho%C5%99e_Olivetsk%C3%A9%2C_N%C3%A1rodn%C3%AD_galerie_v_Praze.jpg/1280px-Olt%C3%A1%C5%99_t%C5%99ebo%C5%88sk%C3%BD%2C_Kristus_na_ho%C5%99e_Olivetsk%C3%A9%2C_N%C3%A1rodn%C3%AD_galerie_v_Praze.jpg</t>
   </si>
   <si>
@@ -511,6 +715,27 @@
     <t>Christ au mont des Oliviers (Retable de Třeboň)</t>
   </si>
   <si>
+    <t>anonyme, actif vers 1380</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Matteo_giovannetti%2C_crocifissione_della_grande_udienza%2C_1353_circa.jpg/1280px-Matteo_giovannetti%2C_crocifissione_della_grande_udienza%2C_1353_circa.jpg</t>
+  </si>
+  <si>
+    <t>Matteo Giovannetti</t>
+  </si>
+  <si>
+    <t>1344-1345</t>
+  </si>
+  <si>
+    <t>Chapelle Saint-Martial, Palais des Papes, Avignon</t>
+  </si>
+  <si>
+    <t>Fresques de la vie de saint Martial</t>
+  </si>
+  <si>
+    <t>actif 1322-1368</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a7/Melchior_Broederlam_004.jpg/1280px-Melchior_Broederlam_004.jpg</t>
   </si>
   <si>
@@ -526,6 +751,9 @@
     <t>Retable de Champmol</t>
   </si>
   <si>
+    <t>actif 1381-1409</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/0/09/Wga_Nardo_di_Cione_Last_Judgment_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
@@ -538,21 +766,24 @@
     <t>Le Jugement dernier (fresque, chapelle Strozzi)</t>
   </si>
   <si>
+    <t>actif vers 1343-1365</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/46/Ni_Zan_-_Six_Gentlemen.jpg/1280px-Ni_Zan_-_Six_Gentlemen.jpg</t>
   </si>
   <si>
     <t>Ni Zan</t>
   </si>
   <si>
-    <t>1345</t>
-  </si>
-  <si>
     <t>Musée de Shanghai, Shanghai</t>
   </si>
   <si>
     <t>Six gentilshommes</t>
   </si>
   <si>
+    <t>1301-1374</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Le_Couronnement_de_la_Vierge_-_Niccolo_di_Pietro_Gerini.jpg/1280px-Le_Couronnement_de_la_Vierge_-_Niccolo_di_Pietro_Gerini.jpg</t>
   </si>
   <si>
@@ -574,6 +805,9 @@
     <t>Pala Feriale</t>
   </si>
   <si>
+    <t>actif vers 1333-vers 1358</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Retablo_de_la_Virgen_de_los_%C3%81ngeles.jpg/1280px-Retablo_de_la_Virgen_de_los_%C3%81ngeles.jpg</t>
   </si>
   <si>
@@ -586,6 +820,9 @@
     <t>La Vierge des Anges (Retable, MNAC)</t>
   </si>
   <si>
+    <t>actif 1357-1406</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e0/Pietro_Cavallini%2C_Vocazione_dei_Santi_Pietro_e_Andrea_%281308-09%29_01.jpg/1280px-Pietro_Cavallini%2C_Vocazione_dei_Santi_Pietro_e_Andrea_%281308-09%29_01.jpg</t>
   </si>
   <si>
@@ -601,6 +838,9 @@
     <t>La Vocation des saints Pierre et André (fresque)</t>
   </si>
   <si>
+    <t>vers 1240-vers 1330</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/53/Pietro_Lorenzetti_-_The_Birth_of_Mary_-_WGA13553.jpg/1280px-Pietro_Lorenzetti_-_The_Birth_of_Mary_-_WGA13553.jpg</t>
   </si>
   <si>
@@ -613,6 +853,9 @@
     <t>Naissance de la Vierge</t>
   </si>
   <si>
+    <t>vers 1280-vers 1348</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Puccio_Capanna_-_Crucifixion_-_WGA04048.jpg/1280px-Puccio_Capanna_-_Crucifixion_-_WGA04048.jpg</t>
   </si>
   <si>
@@ -628,6 +871,9 @@
     <t>Crucifixion</t>
   </si>
   <si>
+    <t>actif vers 1340 (dates incertaines)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Qian_Xuan_-_Early_Autumn_-_29.1_-_Detroit_Institute_of_Arts.jpg/1280px-Qian_Xuan_-_Early_Autumn_-_29.1_-_Detroit_Institute_of_Arts.jpg</t>
   </si>
   <si>
@@ -643,6 +889,15 @@
     <t>Automne précoce (Early Autumn)</t>
   </si>
   <si>
+    <t>vers 1235-avant 1307</t>
+  </si>
+  <si>
+    <t>Encre et couleurs sur papier (rouleau)</t>
+  </si>
+  <si>
+    <t>26,3 × 786 cm</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/47/Simone_dei_crocifissi%2C_madonna_dell%27umilt%C3%A0_tra_angeli%2C_1355-90_ca.jpg/1280px-Simone_dei_crocifissi%2C_madonna_dell%27umilt%C3%A0_tra_angeli%2C_1355-90_ca.jpg</t>
   </si>
   <si>
@@ -658,6 +913,9 @@
     <t>Madone de l'Humilité entourée d'anges</t>
   </si>
   <si>
+    <t>vers 1330-1399</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Simone_Martini_and_Lippo_Memmi_-_Annunciazione_-_Google_Art_Project.jpg/1280px-Simone_Martini_and_Lippo_Memmi_-_Annunciazione_-_Google_Art_Project.jpg</t>
   </si>
   <si>
@@ -670,6 +928,15 @@
     <t>L'Annonciation avec deux saints</t>
   </si>
   <si>
+    <t>vers 1284-1344</t>
+  </si>
+  <si>
+    <t>Tempera et or sur bois</t>
+  </si>
+  <si>
+    <t>184 × 210 cm</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/70/San_Miniato_al_Monte_%28Florence%29_-_Spinello_Aretino_fresco_1.JPG/1280px-San_Miniato_al_Monte_%28Florence%29_-_Spinello_Aretino_fresco_1.JPG</t>
   </si>
   <si>
@@ -685,6 +952,9 @@
     <t>Fresques de la sacristie (Vie de saint Benoît)</t>
   </si>
   <si>
+    <t>vers 1350-1410</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Taddeo_Gaddi%2C_Fresco_cycle_on_the_life_of_the_Virgin%2C_1328-38%3B_Baroncelli_Chapel%2C_Basilica_of_Santa_Croce%2C_Florence_%286%29.jpg/1280px-Taddeo_Gaddi%2C_Fresco_cycle_on_the_life_of_the_Virgin%2C_1328-38%3B_Baroncelli_Chapel%2C_Basilica_of_Santa_Croce%2C_Florence_%286%29.jpg</t>
   </si>
   <si>
@@ -697,6 +967,9 @@
     <t>Fresques de la chapelle Baroncelli</t>
   </si>
   <si>
+    <t>vers 1290-1366</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Mistr_Theodorik%2C_Sv._Luk%C3%A1%C5%A1_Evangelista%2C_N%C3%A1rodn%C3%AD_galerie_v_Praze.jpg/1280px-Mistr_Theodorik%2C_Sv._Luk%C3%A1%C5%A1_Evangelista%2C_N%C3%A1rodn%C3%AD_galerie_v_Praze.jpg</t>
   </si>
   <si>
@@ -712,6 +985,9 @@
     <t>Saint Luc l'Évangéliste</t>
   </si>
   <si>
+    <t>actif 1359-1381</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Feofan_Grek_-_Madonna_of_Don_Icon_-_WGA22207.jpg/1280px-Feofan_Grek_-_Madonna_of_Don_Icon_-_WGA22207.jpg</t>
   </si>
   <si>
@@ -727,6 +1003,9 @@
     <t>Icône Notre-Dame du Don</t>
   </si>
   <si>
+    <t>vers 1340-vers 1410</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg/1280px-Tommaso_da_modena%2C_ritratti_di_domenicani_%28il_cardinale_di_rouen%29_1352_150cm%2C_treviso%2C_ex_convento_di_san_niccol%C3%B2%2C_sala_del_capitolo.jpg</t>
   </si>
   <si>
@@ -742,6 +1021,9 @@
     <t>Portrait du cardinal Hugues de Saint-Cher</t>
   </si>
   <si>
+    <t>1326-1379</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/44/Christ_on_the_Cross_between_the_Virgin_and_Saint_John%2C_Ugolino_di_Nerio%2C_called_Ugolino_da_Siena%2C_c._1330-1335_AD%2C_tempera_on_wood_-_Museo_Nacional_Centro_de_Arte_Reina_Sof%C3%ADa_-_Madrid%2C_Spain_-_DSC08531.JPG/1280px-Christ_on_the_Cross_between_the_Virgin_and_Saint_John%2C_Ugolino_di_Nerio%2C_called_Ugolino_da_Siena%2C_c._1330-1335_AD%2C_tempera_on_wood_-_Museo_Nacional_Centro_de_Arte_Reina_Sof%C3%ADa_-_Madrid%2C_Spain_-_DSC08531.JPG</t>
   </si>
   <si>
@@ -757,6 +1039,9 @@
     <t>Le Christ en croix entre la Vierge et saint Jean</t>
   </si>
   <si>
+    <t>actif vers 1317-vers 1339</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f7/Museo_Davia_Bargellini_-_Madonna_dei_Denti_%28Vitale_da_Bologna%29.jpg/1280px-Museo_Davia_Bargellini_-_Madonna_dei_Denti_%28Vitale_da_Bologna%29.jpg</t>
   </si>
   <si>
@@ -769,6 +1054,9 @@
     <t>Vierge à l'Enfant avec le petit oiseau (Madonna dei Denti)</t>
   </si>
   <si>
+    <t>vers 1309-1359</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/Wang_Meng_Dwelling_in_the_Qingbian_Mountains._ink_on_paper._1366._141x42%2C2_cm._Shanghai_Museum.jpg/1280px-Wang_Meng_Dwelling_in_the_Qingbian_Mountains._ink_on_paper._1366._141x42%2C2_cm._Shanghai_Museum.jpg</t>
   </si>
   <si>
@@ -781,6 +1069,12 @@
     <t>Habitation dans les monts Qingbian</t>
   </si>
   <si>
+    <t>vers 1308-1385</t>
+  </si>
+  <si>
+    <t>141 × 42,2 cm</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Wu_Zhen._Fishermen%2C_detail._35%2C2x332cm._1345._Shanghai_Museum.jpg/1280px-Wu_Zhen._Fishermen%2C_detail._35%2C2x332cm._1345._Shanghai_Museum.jpg</t>
   </si>
   <si>
@@ -790,6 +1084,9 @@
     <t>Les Pêcheurs</t>
   </si>
   <si>
+    <t>1280-1354</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f2/5_Zhao_Mengfu_Monk_in_a_Red_Robe%2C_dated_1304_%2826_x_52_cm%29Liaoning_Provincial_Museum.jpg/1280px-5_Zhao_Mengfu_Monk_in_a_Red_Robe%2C_dated_1304_%2826_x_52_cm%29Liaoning_Provincial_Museum.jpg</t>
   </si>
   <si>
@@ -805,68 +1102,20 @@
     <t>Moine en robe rouge</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Francesco_Traini_Pisa_01.JPG</t>
-  </si>
-  <si>
-    <t>Francesco Traini</t>
-  </si>
-  <si>
-    <t>Museo Nazionale di San Matteo, Pise</t>
-  </si>
-  <si>
-    <t>Polyptyque de San Domenico (avec saint Dominique)</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG/1280px-Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG</t>
-  </si>
-  <si>
-    <t>Guariento di Arpo</t>
-  </si>
-  <si>
-    <t>1344</t>
-  </si>
-  <si>
-    <t>Norton Simon Museum, Pasadena</t>
-  </si>
-  <si>
-    <t>Le Couronnement de la Vierge (retable)</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Matteo_giovannetti%2C_crocifissione_della_grande_udienza%2C_1353_circa.jpg/1280px-Matteo_giovannetti%2C_crocifissione_della_grande_udienza%2C_1353_circa.jpg</t>
-  </si>
-  <si>
-    <t>Matteo Giovannetti</t>
-  </si>
-  <si>
-    <t>1344-1345</t>
-  </si>
-  <si>
-    <t>Chapelle Saint-Martial, Palais des Papes, Avignon</t>
-  </si>
-  <si>
-    <t>Fresques de la vie de saint Martial</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Jean_De_Beaumetz_-_Christ_on_the_Cross_with_a_Carthusian_Monk_-_WGA11944.jpg/1280px-Jean_De_Beaumetz_-_Christ_on_the_Cross_with_a_Carthusian_Monk_-_WGA11944.jpg</t>
-  </si>
-  <si>
-    <t>Jean de Beaumetz</t>
-  </si>
-  <si>
-    <t>1389-1395</t>
-  </si>
-  <si>
-    <t>Cleveland Museum of Art</t>
-  </si>
-  <si>
-    <t>Calvaire avec un moine chartreux</t>
+    <t>1254-1322</t>
+  </si>
+  <si>
+    <t>Encre et couleurs sur papier</t>
+  </si>
+  <si>
+    <t>26 × 52 cm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -886,29 +1135,46 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Carlito"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -917,12 +1183,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC54F38"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -954,13 +1216,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1264,1057 +1534,1603 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="46.85546875" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
+    <col min="1" max="1" width="46.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18" style="1" customWidth="1"/>
+    <col min="4" max="4" width="48" style="1" customWidth="1"/>
+    <col min="5" max="5" width="55" style="1" customWidth="1"/>
+    <col min="6" max="6" width="44.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" s="7" customFormat="1" ht="24.95" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="E34" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="H34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="D60" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="H60" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>256</v>
+        <v>355</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>356</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>258</v>
+        <v>357</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>259</v>
+        <v>358</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>260</v>
+        <v>359</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E61">
-    <sortCondition ref="B2:B61"/>
-  </sortState>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A3" r:id="rId2" display="https://upload.wikimedia.org/wikipedia/commons/thumb/6/63/An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg/960px-An_Angel_offering_a_City_to_the_Prophet._Miraj-nama._1360-1370%2C_Tabriz_%28Topkapi%2C_H.2154%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/quizzes/peinture-14e-niveau2.xlsx
+++ b/quizzes/peinture-14e-niveau2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDD76A30-6AFE-4C96-B470-6DCC49A13A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1440740-3AD1-4E6A-9380-2EEE778494ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -364,9 +364,6 @@
     <t>catalane (Espagne)</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Francesco_Traini_Pisa_01.JPG</t>
-  </si>
-  <si>
     <t>Francesco Traini</t>
   </si>
   <si>
@@ -433,9 +430,6 @@
     <t>actif 1349-vers 1391</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e4/Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG/1280px-Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG</t>
-  </si>
-  <si>
     <t>Guariento di Arpo</t>
   </si>
   <si>
@@ -514,9 +508,6 @@
     <t>actif 1358-vers 1389</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Jean_De_Beaumetz_-_Christ_on_the_Cross_with_a_Carthusian_Monk_-_WGA11944.jpg/1280px-Jean_De_Beaumetz_-_Christ_on_the_Cross_with_a_Carthusian_Monk_-_WGA11944.jpg</t>
-  </si>
-  <si>
     <t>Jean de Beaumetz</t>
   </si>
   <si>
@@ -748,9 +739,6 @@
     <t>anonyme, actif vers 1380</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4c/Matteo_giovannetti%2C_crocifissione_della_grande_udienza%2C_1353_circa.jpg/1280px-Matteo_giovannetti%2C_crocifissione_della_grande_udienza%2C_1353_circa.jpg</t>
-  </si>
-  <si>
     <t>Matteo Giovannetti</t>
   </si>
   <si>
@@ -1145,6 +1133,18 @@
   </si>
   <si>
     <t>26 × 52 cm</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f9/Chapelle_saint_Martial_-_mur_ouest_et_porte.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG/1280px-Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/e8/Francesco_Traini_-_Polittico_di_San_Domenico_-_Museo_San_Matteo_Siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/68/Jean_De_Beaumetz_-_Christ_on_the_Cross_with_a_Carthusian_Monk_-_WGA11944.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1267,6 +1267,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1573,7 +1574,7 @@
   <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="46.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="79.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="1" customWidth="1"/>
     <col min="4" max="4" width="48" style="1" customWidth="1"/>
@@ -2074,23 +2075,23 @@
       </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>33</v>
@@ -2104,22 +2105,22 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>15</v>
@@ -2133,22 +2134,22 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>33</v>
@@ -2162,22 +2163,22 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>15</v>
@@ -2190,23 +2191,23 @@
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>142</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>33</v>
@@ -2220,51 +2221,51 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="G23" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="I23" t="s">
         <v>149</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I23" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>157</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>33</v>
@@ -2278,22 +2279,22 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="F25" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>33</v>
@@ -2306,29 +2307,29 @@
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="I26" t="s">
         <v>53</v>
@@ -2336,25 +2337,25 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="F27" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="G27" s="1" t="s">
         <v>175</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>52</v>
@@ -2365,51 +2366,51 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="F28" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="G28" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>185</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I28" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="F29" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>15</v>
@@ -2423,13 +2424,13 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>74</v>
@@ -2452,22 +2453,22 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="F31" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>33</v>
@@ -2481,51 +2482,51 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="F32" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="I32" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="F33" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>15</v>
@@ -2539,22 +2540,22 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>15</v>
@@ -2568,22 +2569,22 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="F35" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>33</v>
@@ -2597,22 +2598,22 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="F36" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>33</v>
@@ -2626,22 +2627,22 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="F37" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>33</v>
@@ -2650,27 +2651,27 @@
         <v>25</v>
       </c>
       <c r="I37" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="F38" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>33</v>
@@ -2679,27 +2680,27 @@
         <v>25</v>
       </c>
       <c r="I38" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>15</v>
@@ -2713,22 +2714,22 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="F40" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>33</v>
@@ -2737,27 +2738,27 @@
         <v>16</v>
       </c>
       <c r="I40" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>15</v>
@@ -2771,42 +2772,42 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="G42" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>74</v>
@@ -2829,22 +2830,22 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>33</v>
@@ -2858,22 +2859,22 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>33</v>
@@ -2887,22 +2888,22 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="F46" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>15</v>
@@ -2916,22 +2917,22 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>33</v>
@@ -2945,22 +2946,22 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="F48" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>33</v>
@@ -2974,51 +2975,51 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="F49" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="G49" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="H49" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="I49" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="F50" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>33</v>
@@ -3032,28 +3033,28 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>74</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="I51" t="s">
         <v>17</v>
@@ -3061,22 +3062,22 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="F52" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>15</v>
@@ -3090,22 +3091,22 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>15</v>
@@ -3119,22 +3120,22 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="F54" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>33</v>
@@ -3148,22 +3149,22 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="F55" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>33</v>
@@ -3172,27 +3173,27 @@
         <v>25</v>
       </c>
       <c r="I55" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="F56" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>15</v>
@@ -3206,22 +3207,22 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="F57" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>33</v>
@@ -3235,22 +3236,22 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>356</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>33</v>
@@ -3264,89 +3265,89 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="G59" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H59" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="I59" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>29</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>25</v>
       </c>
       <c r="I60" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="F61" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="G61" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="H61" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="I61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3407,6 +3408,10 @@
     <hyperlink ref="A59" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
     <hyperlink ref="A60" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
     <hyperlink ref="A61" r:id="rId56" display="https://upload.wikimedia.org/wikipedia/commons/thumb/b/b2/Autumn_Colors_on_the_Qiao_and_Hua_Mountains_%28cropped%29.jpg/1280px-Autumn_Colors_on_the_Qiao_and_Hua_Mountains_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="A39" r:id="rId57" xr:uid="{D4A40FD8-60B1-4B8C-8424-698095FF2929}"/>
+    <hyperlink ref="A22" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG/1280px-Coronation_of_the_Virgin_Altarpiece_by_Guariento_di_Arpo%2C_1344%2C_Norton_Simon_Museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{112D881E-D0A1-48FB-9361-605DF9724D6C}"/>
+    <hyperlink ref="A18" r:id="rId59" xr:uid="{1F059A8E-0E1A-4685-89C9-0C41351ECBCF}"/>
+    <hyperlink ref="A26" r:id="rId60" xr:uid="{8DBA3C92-A8C0-4FF3-9545-5695A90CF343}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
